--- a/examples/hello-table/fixtures/finance.openpyxl-edited.xlsx
+++ b/examples/hello-table/fixtures/finance.openpyxl-edited.xlsx
@@ -9,11 +9,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ox_3f1c2a90_0000_4c1e_9a00_000000000011" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000011">'Q3'!$A$1</definedName>
-    <definedName name="ox_3f1c2a90_0000_4c1e_9a00_000000000012" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000012">'Q3'!$A$1:$B$4</definedName>
-    <definedName name="ox_3f1c2a90_0000_4c1e_9a00_000000000013" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000013">'Q3'!$B$5</definedName>
-    <definedName name="ox_workbook">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
-    <definedName name="ox_revision">"3b0b95b52b828de91bcdb13f"</definedName>
+    <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000011" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000011">'Q3'!$A$1</definedName>
+    <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000012" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000012">'Q3'!$A$1:$B$4</definedName>
+    <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000013" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000013">'Q3'!$B$5</definedName>
+    <definedName name="mleaf_workbook">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
+    <definedName name="mleaf_revision">"3b0b95b52b828de91bcdb13f"</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>

--- a/examples/hello-table/fixtures/finance.openpyxl-edited.xlsx
+++ b/examples/hello-table/fixtures/finance.openpyxl-edited.xlsx
@@ -13,7 +13,7 @@
     <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000012" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000012">'Q3'!$A$1:$B$4</definedName>
     <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000013" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000013">'Q3'!$B$5</definedName>
     <definedName name="mleaf_workbook">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
-    <definedName name="mleaf_revision">"3b0b95b52b828de91bcdb13f"</definedName>
+    <definedName name="mleaf_revision">"c50ea0fe36a3631b2dbab632"</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -264,6 +264,10 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
